--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484169_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484169_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>X. ANDREU GARI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7574</v>
+        <v>4.1406</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7224</v>
+        <v>5.5664</v>
       </c>
       <c r="F2" t="n">
-        <v>1.035</v>
+        <v>-1.4258</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9156</v>
+        <v>6.6002</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4992</v>
+        <v>0.1757</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4147</v>
+        <v>6.4245</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4332</v>
+        <v>7.1004</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6059</v>
+        <v>0.4234</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.0391</v>
+        <v>6.677</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4823</v>
+        <v>-0.5002</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1067</v>
+        <v>-0.2477</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3756</v>
+        <v>-0.2526</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9919</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3916</v>
+        <v>-0.3883</v>
       </c>
       <c r="T2" t="n">
-        <v>1.933</v>
+        <v>0.4535</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5414</v>
+        <v>-0.8418</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2895</v>
+        <v>-1.2777</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4129</v>
+        <v>0.1947</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1234</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4267</v>
+        <v>3.0044</v>
       </c>
       <c r="E3" t="n">
-        <v>2.191</v>
+        <v>2.0492</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2357</v>
+        <v>0.9552</v>
       </c>
       <c r="G3" t="n">
         <v>0.8736</v>
@@ -688,13 +688,13 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5134</v>
+        <v>1.0911</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6859</v>
+        <v>0.5442</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8274</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>-0.7458</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. ANDREU GARI</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0314</v>
+        <v>2.9398</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6255</v>
+        <v>1.7645</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5941</v>
+        <v>1.1753</v>
       </c>
       <c r="G4" t="n">
-        <v>6.6002</v>
+        <v>-0.9156</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1757</v>
+        <v>0.4992</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4245</v>
+        <v>-1.4147</v>
       </c>
       <c r="J4" t="n">
-        <v>7.1004</v>
+        <v>-0.4332</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4234</v>
+        <v>0.6059</v>
       </c>
       <c r="L4" t="n">
-        <v>6.677</v>
+        <v>-1.0391</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5002</v>
+        <v>-0.4823</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2477</v>
+        <v>-0.1067</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2526</v>
+        <v>-0.3756</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1822</v>
+        <v>-1.1903</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4975</v>
+        <v>0.5739</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4874</v>
+        <v>0.975</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0101</v>
+        <v>-0.4012</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2777</v>
+        <v>2.2895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1947</v>
+        <v>2.4129</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4724</v>
+        <v>-0.1234</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8529</v>
+        <v>1.5517</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4984</v>
+        <v>1.1129</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3546</v>
+        <v>0.4387</v>
       </c>
       <c r="G5" t="n">
         <v>0.7514</v>
@@ -844,13 +844,13 @@
         <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2918</v>
+        <v>0.9905</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6155</v>
+        <v>1.2301</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3237</v>
+        <v>-0.2395</v>
       </c>
       <c r="V5" t="n">
         <v>0.6032</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. COLL JANER</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1887</v>
+        <v>1.1257</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3598</v>
+        <v>1.3709</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.171</v>
+        <v>-0.2452</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5770999999999999</v>
+        <v>1.7512</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5395</v>
+        <v>0.3326</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0376</v>
+        <v>1.4187</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0229</v>
+        <v>2.6466</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0605</v>
+        <v>0.7163</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0376</v>
+        <v>1.9303</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6</v>
+        <v>-0.8953</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6</v>
+        <v>-0.3837</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.5117</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2221</v>
+        <v>0.6603</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1224</v>
+        <v>0.3232</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0998</v>
+        <v>0.3372</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9405</v>
+        <v>-1.881</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2065</v>
+        <v>-0.4085</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>M. COLL JANER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8134</v>
+        <v>0.9614</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0025</v>
+        <v>1.0763</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1891</v>
+        <v>-0.1149</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7512</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3326</v>
+        <v>-0.5395</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4187</v>
+        <v>-0.0376</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6466</v>
+        <v>0.0229</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7163</v>
+        <v>0.0605</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9303</v>
+        <v>-0.0376</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8953</v>
+        <v>-0.6</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3837</v>
+        <v>-0.6</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5117</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.3968</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.5952</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.1903</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.7855</v>
-      </c>
       <c r="S7" t="n">
-        <v>0.348</v>
+        <v>0.9948</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0452</v>
+        <v>0.8389</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3933</v>
+        <v>0.1559</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.881</v>
+        <v>0.9405</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.4085</v>
+        <v>1.2065</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8985</v>
+        <v>-0.6486</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5017</v>
+        <v>-0.1957</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3968</v>
+        <v>-0.4529</v>
       </c>
       <c r="G8" t="n">
         <v>1.2272</v>
@@ -1078,13 +1078,13 @@
         <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3322</v>
+        <v>-0.0822</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0452</v>
+        <v>0.2608</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2869</v>
+        <v>-0.343</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6032</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-1.4053</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2359</v>
+        <v>0.2189</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2314</v>
+        <v>-1.6242</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8369</v>
@@ -1156,13 +1156,13 @@
         <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>1.909</v>
+        <v>1.4992</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9353</v>
+        <v>0.9183</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9737</v>
+        <v>0.5809</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4724</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.138</v>
+        <v>-1.8972</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2256</v>
+        <v>-1.2653</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9124</v>
+        <v>-0.6318</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5802</v>
@@ -1234,13 +1234,13 @@
         <v>1.5871</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0454</v>
+        <v>0.2863</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5726</v>
+        <v>0.5329</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5272</v>
+        <v>-0.2467</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2065</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>A. ELLENA VICENTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6706</v>
+        <v>-2.5225</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.345</v>
+        <v>-0.487</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3256</v>
+        <v>-2.0355</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9021</v>
+        <v>-2.8011</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.635</v>
+        <v>-0.7812</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2671</v>
+        <v>-2.0199</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2397</v>
+        <v>-1.0652</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6399</v>
+        <v>0.2876</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5999</v>
+        <v>-1.3527</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6623</v>
+        <v>-1.736</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0049</v>
+        <v>-1.0688</v>
       </c>
       <c r="O11" t="n">
         <v>-0.6672</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0249</v>
+        <v>0.8899</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1133</v>
+        <v>0.5782</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1383</v>
+        <v>0.3117</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ELLENA VICENTE</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5757</v>
+        <v>-2.5227</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4279</v>
+        <v>-2.1409</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1478</v>
+        <v>-0.3818</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8011</v>
+        <v>-1.9021</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7812</v>
+        <v>-0.635</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0199</v>
+        <v>-1.2671</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0652</v>
+        <v>-1.2397</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2876</v>
+        <v>-0.6399</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3527</v>
+        <v>-0.5999</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.736</v>
+        <v>-0.6623</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0688</v>
+        <v>0.0049</v>
       </c>
       <c r="O12" t="n">
         <v>-0.6672</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5952</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q12" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1729</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.0822</v>
+      </c>
+      <c r="V12" t="n">
         <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.5952</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-0.1632</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-0.3627</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.1995</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-1.2065</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.792200000000001</v>
+        <v>4.7273</v>
       </c>
       <c r="E13" t="n">
-        <v>8.135299999999997</v>
+        <v>9.070199999999998</v>
       </c>
       <c r="F13" t="n">
         <v>-4.3429</v>
@@ -1447,19 +1447,19 @@
         <v>4.541700000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>9.1328</v>
+        <v>9.132800000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-10.0833</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.8696</v>
+        <v>-4.869599999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-5.214200000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9917999999999998</v>
+        <v>-0.9917999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.8787</v>
@@ -1468,16 +1468,16 @@
         <v>13.8871</v>
       </c>
       <c r="S13" t="n">
-        <v>5.753299999999999</v>
+        <v>6.6884</v>
       </c>
       <c r="T13" t="n">
-        <v>5.810899999999999</v>
+        <v>6.745799999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.05730000000000013</v>
+        <v>-0.05740000000000017</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.5599</v>
+        <v>-4.559900000000001</v>
       </c>
       <c r="W13" t="n">
         <v>3.529</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>P. PARISI TRIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3292</v>
+        <v>3.0056</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1374</v>
+        <v>2.6199</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1918</v>
+        <v>0.3856</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3715</v>
+        <v>-0.1107</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.8116</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4367</v>
+        <v>0.7009</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8652</v>
+        <v>0.9207</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1825</v>
+        <v>-0.2918</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6827</v>
+        <v>1.2125</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4937</v>
+        <v>-1.0314</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2477</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2461</v>
+        <v>-0.5117</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8468</v>
+        <v>0.2409</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9467</v>
+        <v>0.2268</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0999</v>
+        <v>0.0141</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6745</v>
+        <v>1.4867</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6745</v>
+        <v>1.4724</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. PARISI TRIA</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0856</v>
+        <v>1.5845</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8037</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2819</v>
+        <v>0.8552</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1107</v>
+        <v>0.3715</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8116</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7009</v>
+        <v>0.4367</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9207</v>
+        <v>0.8652</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2918</v>
+        <v>0.1825</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2125</v>
+        <v>0.6827</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0314</v>
+        <v>-0.4937</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.2477</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5117</v>
+        <v>-0.2461</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6791</v>
+        <v>0.102</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5894</v>
+        <v>0.5386</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0897</v>
+        <v>-0.4366</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4867</v>
+        <v>-0.6745</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4724</v>
+        <v>-0.6745</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MONTALVO PEREZ</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5067</v>
+        <v>1.0568</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7153</v>
+        <v>0.1697</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2086</v>
+        <v>0.8871</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3238</v>
+        <v>-1.4682</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3485</v>
+        <v>-0.6649</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0247</v>
+        <v>-0.8032</v>
       </c>
       <c r="J16" t="n">
-        <v>2.701</v>
+        <v>-0.1121</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5404</v>
+        <v>-0.0796</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1606</v>
+        <v>-0.0325</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3772</v>
+        <v>-1.356</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1918</v>
+        <v>-0.5853</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1853</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7799</v>
+        <v>-0.6957</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7483</v>
+        <v>-0.2663</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0317</v>
+        <v>-0.4295</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1922</v>
+        <v>2.4272</v>
       </c>
       <c r="W16" t="n">
-        <v>0.266</v>
+        <v>1.7384</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4582</v>
+        <v>0.6888</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>A. MONTALVO PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.182</v>
+        <v>0.8401</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0677</v>
+        <v>3.0011</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1143</v>
+        <v>-2.1609</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4682</v>
+        <v>1.3238</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6649</v>
+        <v>2.3485</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8032</v>
+        <v>-1.0247</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1121</v>
+        <v>2.701</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0796</v>
+        <v>2.5404</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0325</v>
+        <v>0.1606</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.356</v>
+        <v>-1.3772</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5853</v>
+        <v>-0.1918</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-1.1853</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5706</v>
+        <v>0.1134</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3683</v>
+        <v>0.0341</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2023</v>
+        <v>0.0793</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4272</v>
+        <v>-1.1922</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7384</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6888</v>
+        <v>-1.4582</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3446</v>
+        <v>0.3739</v>
       </c>
       <c r="E18" t="n">
-        <v>2.397</v>
+        <v>2.7031</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7415</v>
+        <v>-2.3292</v>
       </c>
       <c r="G18" t="n">
         <v>0.8465</v>
@@ -1858,13 +1858,13 @@
         <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7883</v>
+        <v>-1.0699</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7481</v>
+        <v>-0.4421</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0402</v>
+        <v>-0.6278</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9899</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5955</v>
+        <v>-0.3914</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2499</v>
+        <v>-0.3621</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6017</v>
@@ -1936,13 +1936,13 @@
         <v>2.7774</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5056</v>
+        <v>-0.4138</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0284</v>
+        <v>0.2325</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5341</v>
+        <v>-0.6463</v>
       </c>
       <c r="V19" t="n">
         <v>0.6669</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2312</v>
+        <v>-1.0391</v>
       </c>
       <c r="E20" t="n">
         <v>-0.7901</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4411</v>
+        <v>-0.2489</v>
       </c>
       <c r="G20" t="n">
         <v>0.1488</v>
@@ -2014,13 +2014,13 @@
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0509</v>
+        <v>-0.8588</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1247</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9262</v>
+        <v>-0.7341</v>
       </c>
       <c r="V20" t="n">
         <v>0.266</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CORTEGANO NAVARRO</t>
+          <t>J. GAVALDA GUILLEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2828</v>
+        <v>-1.2127</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2748</v>
+        <v>-1.3717</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5575</v>
+        <v>0.1591</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0293</v>
+        <v>-0.119</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1146</v>
+        <v>0.4886</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9147</v>
+        <v>-0.6075</v>
       </c>
       <c r="J21" t="n">
-        <v>4.7999</v>
+        <v>0.1813</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3048</v>
+        <v>0.1411</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4951</v>
+        <v>0.0402</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7706</v>
+        <v>-0.3003</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1902</v>
+        <v>0.3474</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5805</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-6.3483</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-8.133699999999999</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9387</v>
+        <v>-1.2286</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3265</v>
+        <v>-0.5611</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3878</v>
+        <v>-0.6675</v>
       </c>
       <c r="V21" t="n">
-        <v>2.0976</v>
+        <v>0.1349</v>
       </c>
       <c r="W21" t="n">
-        <v>3.2821</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1846</v>
+        <v>0.1349</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3037</v>
+        <v>-1.2519</v>
       </c>
       <c r="E22" t="n">
         <v>-0.9448</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3589</v>
+        <v>-0.3071</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4233</v>
@@ -2170,13 +2170,13 @@
         <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2772</v>
+        <v>-0.2253</v>
       </c>
       <c r="T22" t="n">
         <v>-0.187</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0902</v>
+        <v>-0.0383</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. GAVALDA GUILLEN</t>
+          <t>A. CORTEGANO NAVARRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.489</v>
+        <v>-1.5668</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3717</v>
+        <v>0.6626</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1172</v>
+        <v>-2.2293</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.119</v>
+        <v>2.0293</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4886</v>
+        <v>1.1146</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6075</v>
+        <v>0.9147</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1813</v>
+        <v>4.7999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1411</v>
+        <v>2.3048</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0402</v>
+        <v>2.4951</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3003</v>
+        <v>-2.7706</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3474</v>
+        <v>-1.1902</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.5805</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-6.3483</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9919</v>
+        <v>-8.133699999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5049</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5611</v>
+        <v>0.7143</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9438</v>
+        <v>-0.0596</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1349</v>
+        <v>2.0976</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.2821</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1349</v>
+        <v>-1.1846</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3991</v>
+        <v>-2.7887</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3507</v>
+        <v>-2.0447</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0484</v>
+        <v>-0.744</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5879</v>
@@ -2326,13 +2326,13 @@
         <v>0.9919</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.3316</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4137</v>
+        <v>-0.1076</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5283</v>
+        <v>-0.224</v>
       </c>
       <c r="V24" t="n">
         <v>0.3373</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.792200000000001</v>
+        <v>-1.7518</v>
       </c>
       <c r="E25" t="n">
-        <v>4.343100000000001</v>
+        <v>4.343</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.135100000000001</v>
+        <v>-6.0945</v>
       </c>
       <c r="G25" t="n">
         <v>-3.5909</v>
@@ -2395,7 +2395,7 @@
         <v>-9.1327</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9919999999999993</v>
+        <v>0.9919999999999992</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.8868</v>
@@ -2404,13 +2404,13 @@
         <v>14.879</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.7532</v>
+        <v>-3.712699999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.05759999999999971</v>
+        <v>0.05749999999999991</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.8108</v>
+        <v>-3.7703</v>
       </c>
       <c r="V25" t="n">
         <v>4.56</v>
